--- a/stories/arbres/TREE-SAN-005.xlsx
+++ b/stories/arbres/TREE-SAN-005.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a école aujourd'hui. Maman est là. Papa aussi. Le matin, on prend la brosse. Le soir, on prend la brosse. Un adulte est avec Léa. C'est maman, ou papa. Les dents aiment la brosse.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1653,6 +1680,11 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Léa se lève. Maman est dans la salle de bain. Un adulte est là. Léa prend sa brosse. Elles brossent. En haut. En bas. Le soir, ce sera pareil. Brosse, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1865,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Léa se brosse. Avec quoi ?</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2038,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a pris la brosse. Le matin, c'est fait. Le soir, elle la reprendra. Un adulte sera là.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2191,6 +2233,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2353,6 +2400,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Léa passe par la cuisine. Elle boit une gorgée. Puis elle prend la brosse. Maman, l'adulte, brosse avec elle. Le matin. Et ce soir, encore la brosse.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2545,6 +2597,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -2709,6 +2766,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Léa prend le ballon rouge. Ses dents sont brossées. Le matin, la brosse. Le soir, la brosse. Un adulte était là.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2871,6 +2933,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3033,6 +3100,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Léa pose le seau bleu. Elle a pris la brosse le matin. Le soir, ce sera pareil, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3195,6 +3267,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3357,6 +3434,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Léa serre le doudou. La brosse est rangée. Matin et soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3519,6 +3601,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3681,6 +3768,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Léa ouvre la porte du jardin. L'air est frais. Puis elle rentre. Elle prend la brosse. Maman, l'adulte, est là. Le matin. Le soir aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3873,6 +3965,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -4037,6 +4134,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Dehors, le ballon rouge attend. Léa a brossé. Matin, brosse. Soir, brosse. Un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4199,6 +4301,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4361,6 +4468,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Léa pose le seau bleu près des fleurs. Elle a pris la brosse. Le matin et le soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4523,6 +4635,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4685,6 +4802,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou reste à la fenêtre. Léa a la brosse. Matin et soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4847,6 +4969,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5009,6 +5136,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Léa revient dans la chambre. Elle s'habille. Puis elle prend la brosse. Papa, l'adulte, l'aide. C'est le matin. Le soir, la brosse reviendra.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5201,6 +5333,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -5365,6 +5502,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Le ballon rouge est sous le lit. Léa a brossé. Le matin, la brosse. Le soir, la brosse. Un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5527,6 +5669,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5689,6 +5836,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Le seau bleu sert aux crayons. Léa a pris la brosse. Matin et soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5851,6 +6003,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6013,6 +6170,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou l'attend. Léa range la brosse. Matin et soir, un adulte est là.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6175,6 +6337,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6337,6 +6504,11 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Léa se réveille. L'école est calme. Maman est venue. Un adulte est là. Léa prend sa brosse. Elles brossent un peu. Le matin, c'était déjà fait. Le soir, on brossera encore.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6513,6 +6685,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Léa prend quoi, après la sieste ?</t>
         </is>
       </c>
     </row>
@@ -6681,6 +6858,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, Léa a brossé. Le matin déjà. Le soir encore. Un adulte avec elle.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6871,6 +7053,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7033,6 +7220,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va à la cuisine. Un verre d'eau. Elle a pris la brosse. Maman, l'adulte, sourit. Le matin. Après la sieste. Le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7225,6 +7417,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -7389,6 +7586,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Léa roule le ballon rouge. La brosse a fait son travail. Matin et soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7551,6 +7753,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7713,6 +7920,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Léa pose le seau bleu. Elle a la brosse. Le matin, le soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7875,6 +8087,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8037,6 +8254,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Léa câline le doudou. Elle a brossé. Matin et soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8199,6 +8421,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8361,6 +8588,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va au jardin un moment. Ses dents sont brossées. Un adulte l'a aidée. Le matin. Le soir, la brosse reviendra.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8553,6 +8785,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -8717,6 +8954,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Le ballon rouge rebondit. Léa a pris la brosse. Matin et soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8879,6 +9121,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9041,6 +9288,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Le seau bleu a de l'eau pour les fleurs. Léa a brossé. Le matin, le soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9203,6 +9455,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9365,6 +9622,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou s'assoit dehors un peu. Léa a la brosse. Matin et soir. Un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9527,6 +9789,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9689,6 +9956,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rentre dans la chambre. Le lit est défait. Elle a pris la brosse. Papa, l'adulte, range. Le matin c'était fait. Le soir, encore.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9881,6 +10153,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -10045,6 +10322,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Le ballon rouge attend. Léa a brossé. Matin et soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10207,6 +10489,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10369,6 +10656,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Le seau bleu est sous la table. Léa a pris la brosse. Le matin, le soir. Un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10531,6 +10823,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10693,6 +10990,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou retrouve l'oreiller. Léa a la brosse. Matin et soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10855,6 +11157,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10879,7 +11186,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. Léa rentre d'école. Papa dit : la brosse. Un adulte est là. Léa prend sa brosse. Ils brossent. Le matin, c'était déjà fait. Matin et soir.</t>
+          <t>C'est le soir. Léa rentre d'école. La brosse. Un adulte est là. Léa prend sa brosse. Ils brossent. Le matin, c'était déjà fait. Matin et soir.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11017,6 +11324,13 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le soir. Léa rentre d'école.
+papa|La brosse.
+narrateur|Un adulte est là. Léa prend sa brosse. Ils brossent. Le matin, c'était déjà fait. Matin et soir.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11197,6 +11511,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, Léa prend quoi ?</t>
         </is>
       </c>
     </row>
@@ -11365,6 +11684,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a brossé le soir. Le matin aussi. Un adulte était avec elle.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11555,6 +11879,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11717,6 +12046,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Léa boit un peu à la cuisine. Puis elle prend la brosse. Papa, l'adulte, brosse aussi. Le soir. Comme le matin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11909,6 +12243,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -12073,6 +12412,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Le ballon rouge reste au salon. Léa a brossé. Le soir et le matin, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12235,6 +12579,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12397,6 +12746,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Le seau bleu reste à sa place. Léa a pris la brosse. Matin et soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12559,6 +12913,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12721,6 +13080,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou va au lit. Léa a la brosse. Le matin, le soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12883,6 +13247,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13045,6 +13414,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Léa ferme la porte du jardin. Il fait nuit. Elle a pris la brosse. Maman, l'adulte, l'aide. Le soir. Le matin, ce sera pareil.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13237,6 +13611,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -13401,6 +13780,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Le ballon rouge dort au panier. Léa a brossé. Matin et soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13563,6 +13947,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13725,6 +14114,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Le seau bleu reste dehors. Léa a pris la brosse. Le soir, le matin, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13887,6 +14281,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14049,6 +14448,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou sent bon. Léa a la brosse. Matin et soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14211,6 +14615,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14373,6 +14782,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Léa est dans la chambre. Pyjama. Elle a déjà pris la brosse. Un adulte était là. Le soir. Le matin aussi.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14565,6 +14979,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
     </row>
@@ -14729,6 +15148,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Le ballon rouge reste au pied du lit. Léa a brossé. Le matin, le soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14891,6 +15315,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15053,6 +15482,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Le seau bleu sert de table de nuit. Léa a pris la brosse. Matin et soir, un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15215,6 +15649,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15377,6 +15816,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Le doudou est sous le coude. Léa a la brosse. Matin et soir, avec un adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15539,6 +15983,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15557,7 +16006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15630,6 +16079,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-SAN-005.xlsx
+++ b/stories/arbres/TREE-SAN-005.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Léa a école aujourd'hui. Maman est là. Papa aussi. Le matin, on prend la brosse. Le soir, on prend la brosse. Un adulte est avec Léa. C'est maman, ou papa. Les dents aiment la brosse.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
           <t>narrateur|C'est le matin. Léa se lève. Maman est dans la salle de bain. Un adulte est là. Léa prend sa brosse. Elles brossent. En haut. En bas. Le soir, ce sera pareil. Brosse, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1872,6 +1880,7 @@
           <t>narrateur|Léa se brosse. Avec quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2043,6 +2052,7 @@
           <t>narrateur|Léa a pris la brosse. Le matin, c'est fait. Le soir, elle la reprendra. Un adulte sera là.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2238,6 +2248,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2405,6 +2416,7 @@
           <t>narrateur|Léa passe par la cuisine. Elle boit une gorgée. Puis elle prend la brosse. Maman, l'adulte, brosse avec elle. Le matin. Et ce soir, encore la brosse.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2604,6 +2616,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2771,6 +2784,7 @@
           <t>narrateur|Léa prend le ballon rouge. Ses dents sont brossées. Le matin, la brosse. Le soir, la brosse. Un adulte était là.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2938,6 +2952,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3105,6 +3120,7 @@
           <t>narrateur|Léa pose le seau bleu. Elle a pris la brosse le matin. Le soir, ce sera pareil, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3272,6 +3288,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3439,6 +3456,7 @@
           <t>narrateur|Léa serre le doudou. La brosse est rangée. Matin et soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3606,6 +3624,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3773,6 +3792,7 @@
           <t>narrateur|Léa ouvre la porte du jardin. L'air est frais. Puis elle rentre. Elle prend la brosse. Maman, l'adulte, est là. Le matin. Le soir aussi.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3972,6 +3992,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4139,6 +4160,7 @@
           <t>narrateur|Dehors, le ballon rouge attend. Léa a brossé. Matin, brosse. Soir, brosse. Un adulte.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4306,6 +4328,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4473,6 +4496,7 @@
           <t>narrateur|Léa pose le seau bleu près des fleurs. Elle a pris la brosse. Le matin et le soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4640,6 +4664,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4807,6 +4832,7 @@
           <t>narrateur|Le doudou reste à la fenêtre. Léa a la brosse. Matin et soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4974,6 +5000,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5141,6 +5168,7 @@
           <t>narrateur|Léa revient dans la chambre. Elle s'habille. Puis elle prend la brosse. Papa, l'adulte, l'aide. C'est le matin. Le soir, la brosse reviendra.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5340,6 +5368,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5507,6 +5536,7 @@
           <t>narrateur|Le ballon rouge est sous le lit. Léa a brossé. Le matin, la brosse. Le soir, la brosse. Un adulte.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5674,6 +5704,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5841,6 +5872,7 @@
           <t>narrateur|Le seau bleu sert aux crayons. Léa a pris la brosse. Matin et soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6008,6 +6040,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6175,6 +6208,7 @@
           <t>narrateur|Le doudou l'attend. Léa range la brosse. Matin et soir, un adulte est là.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6342,6 +6376,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6509,6 +6544,7 @@
           <t>narrateur|Après la sieste, Léa se réveille. L'école est calme. Maman est venue. Un adulte est là. Léa prend sa brosse. Elles brossent un peu. Le matin, c'était déjà fait. Le soir, on brossera encore.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6692,6 +6728,7 @@
           <t>narrateur|Léa prend quoi, après la sieste ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6863,6 +6900,7 @@
           <t>narrateur|Après la sieste, Léa a brossé. Le matin déjà. Le soir encore. Un adulte avec elle.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7058,6 +7096,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7225,6 +7264,7 @@
           <t>narrateur|Léa va à la cuisine. Un verre d'eau. Elle a pris la brosse. Maman, l'adulte, sourit. Le matin. Après la sieste. Le soir.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7424,6 +7464,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7591,6 +7632,7 @@
           <t>narrateur|Léa roule le ballon rouge. La brosse a fait son travail. Matin et soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7758,6 +7800,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7925,6 +7968,7 @@
           <t>narrateur|Léa pose le seau bleu. Elle a la brosse. Le matin, le soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8092,6 +8136,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8259,6 +8304,7 @@
           <t>narrateur|Léa câline le doudou. Elle a brossé. Matin et soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8426,6 +8472,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8593,6 +8640,7 @@
           <t>narrateur|Léa va au jardin un moment. Ses dents sont brossées. Un adulte l'a aidée. Le matin. Le soir, la brosse reviendra.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8792,6 +8840,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8959,6 +9008,7 @@
           <t>narrateur|Le ballon rouge rebondit. Léa a pris la brosse. Matin et soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9126,6 +9176,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9293,6 +9344,7 @@
           <t>narrateur|Le seau bleu a de l'eau pour les fleurs. Léa a brossé. Le matin, le soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9460,6 +9512,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9627,6 +9680,7 @@
           <t>narrateur|Le doudou s'assoit dehors un peu. Léa a la brosse. Matin et soir. Un adulte.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9794,6 +9848,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9961,6 +10016,7 @@
           <t>narrateur|Léa rentre dans la chambre. Le lit est défait. Elle a pris la brosse. Papa, l'adulte, range. Le matin c'était fait. Le soir, encore.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10160,6 +10216,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10327,6 +10384,7 @@
           <t>narrateur|Le ballon rouge attend. Léa a brossé. Matin et soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10494,6 +10552,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10661,6 +10720,7 @@
           <t>narrateur|Le seau bleu est sous la table. Léa a pris la brosse. Le matin, le soir. Un adulte.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10828,6 +10888,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10995,6 +11056,7 @@
           <t>narrateur|Le doudou retrouve l'oreiller. Léa a la brosse. Matin et soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11162,6 +11224,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11331,6 +11394,7 @@
 narrateur|Un adulte est là. Léa prend sa brosse. Ils brossent. Le matin, c'était déjà fait. Matin et soir.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11518,6 +11582,7 @@
           <t>narrateur|Le soir, Léa prend quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11689,6 +11754,7 @@
           <t>narrateur|Léa a brossé le soir. Le matin aussi. Un adulte était avec elle.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11884,6 +11950,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12051,6 +12118,7 @@
           <t>narrateur|Léa boit un peu à la cuisine. Puis elle prend la brosse. Papa, l'adulte, brosse aussi. Le soir. Comme le matin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12250,6 +12318,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12417,6 +12486,7 @@
           <t>narrateur|Le ballon rouge reste au salon. Léa a brossé. Le soir et le matin, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12584,6 +12654,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12751,6 +12822,7 @@
           <t>narrateur|Le seau bleu reste à sa place. Léa a pris la brosse. Matin et soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12918,6 +12990,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13085,6 +13158,7 @@
           <t>narrateur|Le doudou va au lit. Léa a la brosse. Le matin, le soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13252,6 +13326,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13419,6 +13494,7 @@
           <t>narrateur|Léa ferme la porte du jardin. Il fait nuit. Elle a pris la brosse. Maman, l'adulte, l'aide. Le soir. Le matin, ce sera pareil.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13618,6 +13694,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13785,6 +13862,7 @@
           <t>narrateur|Le ballon rouge dort au panier. Léa a brossé. Matin et soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13952,6 +14030,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14119,6 +14198,7 @@
           <t>narrateur|Le seau bleu reste dehors. Léa a pris la brosse. Le soir, le matin, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14286,6 +14366,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14453,6 +14534,7 @@
           <t>narrateur|Le doudou sent bon. Léa a la brosse. Matin et soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14620,6 +14702,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14787,6 +14870,7 @@
           <t>narrateur|Léa est dans la chambre. Pyjama. Elle a déjà pris la brosse. Un adulte était là. Le soir. Le matin aussi.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14986,6 +15070,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15153,6 +15238,7 @@
           <t>narrateur|Le ballon rouge reste au pied du lit. Léa a brossé. Le matin, le soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15320,6 +15406,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15487,6 +15574,7 @@
           <t>narrateur|Le seau bleu sert de table de nuit. Léa a pris la brosse. Matin et soir, un adulte.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15654,6 +15742,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15821,6 +15910,7 @@
           <t>narrateur|Le doudou est sous le coude. Léa a la brosse. Matin et soir, avec un adulte.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15988,6 +16078,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16006,7 +16097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16086,6 +16177,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16100,7 +16205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16287,6 +16392,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
